--- a/results_fedavg_dirichlet_4class/client_detail_per_round.xlsx
+++ b/results_fedavg_dirichlet_4class/client_detail_per_round.xlsx
@@ -486,41 +486,41 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>131</v>
+        <v>367</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2134</v>
+        <v>0.5977</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>98.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>36.5%</t>
         </is>
       </c>
     </row>
@@ -574,41 +574,41 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>367</v>
+        <v>131</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5977</v>
+        <v>0.2134</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -618,14 +618,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>116</v>
+        <v>367</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1889</v>
+        <v>0.5977</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -633,26 +633,26 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
     </row>
@@ -706,41 +706,41 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>367</v>
+        <v>116</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5977</v>
+        <v>0.1889</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>96.8%</t>
+          <t>95.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
     </row>
@@ -750,41 +750,41 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2134</v>
+        <v>0.1889</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.9%</t>
         </is>
       </c>
     </row>
@@ -794,14 +794,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>116</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1889</v>
+        <v>0.5977</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -809,26 +809,26 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
     </row>
@@ -838,41 +838,41 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>367</v>
+        <v>131</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5977</v>
+        <v>0.2134</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>95.2%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -882,41 +882,41 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>367</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5977</v>
+        <v>0.2134</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>91.3%</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -926,41 +926,41 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2134</v>
+        <v>0.1889</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>91.3%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>0.9%</t>
         </is>
       </c>
     </row>
@@ -970,41 +970,41 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>367</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1889</v>
+        <v>0.5977</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>21</v>
+        <v>62</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>36.5%</t>
         </is>
       </c>
     </row>
@@ -1014,41 +1014,41 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>C2</t>
+          <t>C3</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1889</v>
+        <v>0.2134</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>95.7%</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>81.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -1058,41 +1058,41 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>C1</t>
+          <t>C2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>367</v>
+        <v>116</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5977</v>
+        <v>0.1889</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>98.4%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>62</v>
+        <v>21</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>0.9%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>16.3%</t>
+          <t>81.0%</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>0.9%</t>
         </is>
       </c>
     </row>
@@ -1102,41 +1102,41 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>C3</t>
+          <t>C1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>131</v>
+        <v>367</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2134</v>
+        <v>0.5977</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>95.7%</t>
+          <t>96.8%</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>86.3%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.3%</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>36.5%</t>
         </is>
       </c>
     </row>
